--- a/hira_material_automation/output/monthly/202601_202606__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__arthroscopy_cannula__041001__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:24:05</t>
+          <t>2026-06-14T22:17:23</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>368f38e15596b383d00c6ba1444a5c351b2325ce1fe7746ba0f5c74e5943bdd5</t>
+          <t>b17594433730fede2f9c68eead5670fdd998d529a390d048a8e5d23708bef662</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__arthroscopy_cannula__041001__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:23</t>
+          <t>2026-06-24T22:22:10</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b17594433730fede2f9c68eead5670fdd998d529a390d048a8e5d23708bef662</t>
+          <t>b5954bcf3177547fe13d050743caa180e23440e9381e3a5aa4906b8c9d31cf17</t>
         </is>
       </c>
     </row>
